--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>
@@ -425,7 +425,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="4">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="4">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="8">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="5">
   <si>
     <t>Country</t>
   </si>
@@ -24,6 +24,9 @@
   </si>
   <si>
     <t>2019</t>
+  </si>
+  <si>
+    <t>2015</t>
   </si>
 </sst>
 </file>
@@ -84,7 +87,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="5">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="5">
   <si>
     <t>Country</t>
   </si>
@@ -87,7 +87,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="6">
   <si>
     <t>Country</t>
   </si>
@@ -27,6 +27,9 @@
   </si>
   <si>
     <t>2015</t>
+  </si>
+  <si>
+    <t>2011</t>
   </si>
 </sst>
 </file>
@@ -87,7 +90,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="6">
   <si>
     <t>Country</t>
   </si>
@@ -90,7 +90,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="6">
   <si>
     <t>Country</t>
   </si>

--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="6">
   <si>
     <t>Country</t>
   </si>
